--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:20</t>
+    <t xml:space="preserve">2026-09-09 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
@@ -59,12 +59,12 @@
     <t xml:space="preserve">Promedio Regional</t>
   </si>
   <si>
+    <t xml:space="preserve">Marga Marga</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillota</t>
   </si>
   <si>
-    <t xml:space="preserve">Marga Marga</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:19</t>
+    <t xml:space="preserve">2026-09-17 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7.35</v>
+        <v>6.74</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -721,7 +721,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5.08</v>
+        <v>5.41</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -755,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6.74</v>
+        <v>7.35</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5.41</v>
+        <v>5.08</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1099,18 +1099,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.16</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="4">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>6</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1183,101 +1183,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.48</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.06</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7.09</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5.16</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.7</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.58</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="11">
@@ -1315,7 +1315,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>32</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>35</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>36</v>
@@ -1414,35 +1414,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4.17</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5.02</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:45</t>
+    <t xml:space="preserve">2026-09-25 21:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -644,7 +644,7 @@
         <v>-0.26</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3.59</v>
+        <v>-3.62</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>7</v>
@@ -667,7 +667,7 @@
         <v>-0.34</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6.28</v>
+        <v>-6.27</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7</v>
@@ -690,7 +690,7 @@
         <v>-0.3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4.85</v>
+        <v>-4.8</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2022_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 23:50</t>
+    <t xml:space="preserve">2026-10-05 07:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
